--- a/Default Resource Keys.xlsx
+++ b/Default Resource Keys.xlsx
@@ -8,70 +8,209 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekdrn\source\repos\Starcraft_Clone_Game_Client\Proj\Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB0115B-9B46-4314-A796-B4956F4ED346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67B00EB-299E-4776-AB9C-05A586AA3FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rasterizer State" sheetId="1" r:id="rId1"/>
+    <sheet name="Rasterizer State" sheetId="5" r:id="rId1"/>
+    <sheet name="Mesh" sheetId="7" r:id="rId2"/>
+    <sheet name="Material" sheetId="9" r:id="rId3"/>
+    <sheet name="GraphicsPipeline" sheetId="8" r:id="rId4"/>
+    <sheet name="Depth Stencil State" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>RSS_Solid_Back</t>
   </si>
   <si>
-    <t>Key</t>
+    <t>D3D11_FILL_SOLID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSS_WireFrame</t>
+  </si>
+  <si>
+    <t>String Key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debug_GraphicsPipeline</t>
+  </si>
+  <si>
+    <t>Debug_Material</t>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디버그용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSS_Default</t>
+  </si>
+  <si>
+    <t>RSS_Solid_Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DepthEnable</t>
+  </si>
+  <si>
+    <t>DepthWriteMask</t>
+  </si>
+  <si>
+    <t>D3D11_DEPTH_WRITE_MASK_ALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 DSS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 RSS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FillMode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CullMode</t>
-  </si>
-  <si>
-    <t>FrontCounterClockwise</t>
-  </si>
-  <si>
-    <t>DepthClipEnable</t>
-  </si>
-  <si>
-    <t>D3D11_FILL_SOLID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3D11_FILL_WIREFRAME</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>D3D11_CULL_BACK</t>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가장 기본적인 RSS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3D11_CULL_NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debug_RectMesh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디버그용 사각형 메쉬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vertex Buffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position(float3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index Buffer Topology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3D11_PRIMITIVE_TOPOLOGY_LINESTRIP</t>
+  </si>
+  <si>
+    <t>Texture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input Layout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixel Shader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vertex Shader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Render Pipeline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rasterizer State</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Depth Stencil State</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blend State</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>RSS_WireFrame</t>
-  </si>
-  <si>
-    <t>디버그용 RSS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D3D11_FILL_WIREFRAME</t>
-  </si>
-  <si>
-    <t>D3D11_CULL_NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSS_Debug</t>
+  </si>
+  <si>
+    <t>디버그용 DSS, 깊이 스텐실 테스트 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite_GraphicsPipeline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D 스프라이트용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSS_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSS_Debug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DepthFunc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3D11_COMPARISON_GREATER_EQUAL (Reversed-Z)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -114,13 +253,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -131,6 +288,59 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{036101DD-724C-4ADA-B0B1-1B270EF12145}" name="표7" displayName="표7" ref="A1:D3" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:D3" xr:uid="{036101DD-724C-4ADA-B0B1-1B270EF12145}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{18796FC0-5226-4DF4-8A21-F28AC5B5E6A4}" name="String Key" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{46998692-8386-45ED-9E54-540F8A4D61A4}" name="Desc"/>
+    <tableColumn id="3" xr3:uid="{50882672-BDA8-4FBE-B52D-D9BD1FBB7B53}" name="FillMode"/>
+    <tableColumn id="4" xr3:uid="{3DAB9361-B055-42EB-ACB4-62144FB22828}" name="CullMode" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9203A391-AF1C-461A-828E-701059761174}" name="표9" displayName="표9" ref="A1:D2" totalsRowShown="0">
+  <autoFilter ref="A1:D2" xr:uid="{9203A391-AF1C-461A-828E-701059761174}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{81E2E411-BC2A-46D5-AB08-BB0A207E5C25}" name="String Key"/>
+    <tableColumn id="2" xr3:uid="{7E8D97C8-E164-4C15-8140-9B59FF6CDDF4}" name="Desc"/>
+    <tableColumn id="3" xr3:uid="{121398F6-0C43-4098-880A-77E08F230736}" name="Vertex Buffer"/>
+    <tableColumn id="4" xr3:uid="{69D58319-68EC-494E-8F5F-18B0B9FB0A11}" name="Index Buffer Topology"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0AFCD8C3-26B4-461D-B084-993121E4A30B}" name="표10" displayName="표10" ref="A1:D2" totalsRowShown="0">
+  <autoFilter ref="A1:D2" xr:uid="{0AFCD8C3-26B4-461D-B084-993121E4A30B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{239E6E71-EC04-4F33-BDA8-8D2A474F3B83}" name="String Key"/>
+    <tableColumn id="2" xr3:uid="{F3822DE1-B22D-418C-B723-D88487F448CA}" name="Description"/>
+    <tableColumn id="3" xr3:uid="{DD00A5B5-230A-45D6-95A9-254A35D68277}" name="Texture"/>
+    <tableColumn id="4" xr3:uid="{4518AEF7-8813-4920-9B04-F63F3ABCC6BD}" name="Render Pipeline"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B697EA02-9D8C-49F3-BBEC-0B34AD3175EA}" name="표5" displayName="표5" ref="A1:E3" totalsRowShown="0">
+  <autoFilter ref="A1:E3" xr:uid="{B697EA02-9D8C-49F3-BBEC-0B34AD3175EA}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1E36A5F8-349A-427B-93EF-1E4346B14905}" name="String Key" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{992AE039-31DB-49D6-B880-288799888481}" name="Desc"/>
+    <tableColumn id="3" xr3:uid="{1DB2B66D-5F42-4C3E-B5A1-0199E3837225}" name="DepthEnable"/>
+    <tableColumn id="4" xr3:uid="{B32E2393-0EDB-42A9-A729-74C46042D89C}" name="DepthWriteMask" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C06B6E7B-14EE-4534-BF60-314B185AA3BF}" name="DepthFunc"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -395,79 +605,298 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6745073-6E54-4A83-B8EA-59C528F76C4E}">
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAFEF60-5061-4DD5-9D94-3F9CA67DA88D}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="16.2109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="37.35546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904A050C-63BA-4BF5-818C-91242FD78D7F}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="14.78515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.35546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2592D615-D54E-4D37-860F-0319F5D96314}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
+      <c r="H3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6815225-49ED-4AFC-8DAF-9449C9736E16}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="30.2109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>